--- a/daily_matches/job_matches_2026-10-18.xlsx
+++ b/daily_matches/job_matches_2026-10-18.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,175 +456,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Warehouse Engineer</t>
+          <t>Data Engineer, Finance (R6329)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Shield AI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Englewood, CO, USA USA</t>
+          <t>San Diego, CA, USA USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, S3, EC2, Glue, Redshift, Data Lake, Apache Airflow</t>
+          <t>Cortex, S3, Snowflake, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50267e1f88400770</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>HealthEdge Software, Inc.</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d11a19f488c0ecd</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Scientist III – AI Scientist for Quantitative Neuropathy and ML Scalable Infrastructure</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ALLEN INSTITUTE</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Seattle, WA, USA USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>10</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Scala, Bayesian</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1e3e6ff21bb5e7bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Software Engineer I</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Planview</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>USA USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Generative AI, Copilot, Docker, CI/CD, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=71520074c21c4715</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Engineer, Agentic Engineering Governance, Open Source</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>College Board</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Remote, USA USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Copilot, S3, EC2, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8aaa98c8c3416fe</t>
+          <t>https://www.indeed.com/viewjob?jk=5f71da028c1e7730</t>
         </is>
       </c>
     </row>
